--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="63">
   <si>
     <t>Materia</t>
   </si>
@@ -65,18 +65,12 @@
     <t>FLORES MIXCOHA CRISTHIAN ALFONSO</t>
   </si>
   <si>
-    <t>GUTIERREZ FLORES MILKA SARAY</t>
-  </si>
-  <si>
     <t>HERNANDEZ ILLESCAS REDA ALAN</t>
   </si>
   <si>
     <t>HERNANDEZ NAJERA ALBERTO SHAKIB</t>
   </si>
   <si>
-    <t>MARTINEZ SANTOS ANGEL GABRIEL</t>
-  </si>
-  <si>
     <t>ORTEGA HERNANDEZ ALEXIS ISAI</t>
   </si>
   <si>
@@ -164,22 +158,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>REYES</t>
@@ -589,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -948,22 +927,22 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1002,22 +981,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1025,22 +1004,22 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>-1</v>
@@ -1079,22 +1058,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1102,13 +1081,13 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1117,7 +1096,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H9">
         <v>-1</v>
@@ -1156,13 +1135,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1171,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1179,22 +1158,22 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1233,22 +1212,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1256,13 +1235,13 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -1271,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1310,13 +1289,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1325,7 +1304,7 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1333,23 +1312,23 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
         <v>8</v>
       </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>9</v>
-      </c>
       <c r="H12">
         <v>-1</v>
       </c>
@@ -1390,19 +1369,19 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V12">
+        <v>5</v>
+      </c>
+      <c r="W12">
+        <v>9</v>
+      </c>
+      <c r="X12">
+        <v>7</v>
+      </c>
+      <c r="Y12">
         <v>8</v>
-      </c>
-      <c r="W12">
-        <v>9</v>
-      </c>
-      <c r="X12">
-        <v>10</v>
-      </c>
-      <c r="Y12">
-        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1410,23 +1389,23 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13">
         <v>7</v>
       </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>9</v>
-      </c>
-      <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
       <c r="H13">
         <v>-1</v>
       </c>
@@ -1467,19 +1446,19 @@
         <v>5</v>
       </c>
       <c r="U13">
+        <v>9</v>
+      </c>
+      <c r="V13">
+        <v>9</v>
+      </c>
+      <c r="W13">
+        <v>9</v>
+      </c>
+      <c r="X13">
+        <v>9</v>
+      </c>
+      <c r="Y13">
         <v>7</v>
-      </c>
-      <c r="V13">
-        <v>5</v>
-      </c>
-      <c r="W13">
-        <v>9</v>
-      </c>
-      <c r="X13">
-        <v>6</v>
-      </c>
-      <c r="Y13">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1487,10 +1466,10 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1499,10 +1478,10 @@
         <v>9</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1544,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1553,10 +1532,10 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1564,13 +1543,13 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1579,53 +1558,53 @@
         <v>9</v>
       </c>
       <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+      <c r="I15">
+        <v>-1</v>
+      </c>
+      <c r="J15">
+        <v>-1</v>
+      </c>
+      <c r="K15">
+        <v>-1</v>
+      </c>
+      <c r="L15">
+        <v>-1</v>
+      </c>
+      <c r="M15">
+        <v>-1</v>
+      </c>
+      <c r="N15">
+        <v>-1</v>
+      </c>
+      <c r="O15">
+        <v>-1</v>
+      </c>
+      <c r="P15">
+        <v>-1</v>
+      </c>
+      <c r="Q15">
+        <v>-1</v>
+      </c>
+      <c r="R15">
+        <v>-1</v>
+      </c>
+      <c r="S15">
+        <v>-1</v>
+      </c>
+      <c r="T15">
+        <v>5</v>
+      </c>
+      <c r="U15">
+        <v>8</v>
+      </c>
+      <c r="V15">
         <v>7</v>
       </c>
-      <c r="H15">
-        <v>-1</v>
-      </c>
-      <c r="I15">
-        <v>-1</v>
-      </c>
-      <c r="J15">
-        <v>-1</v>
-      </c>
-      <c r="K15">
-        <v>-1</v>
-      </c>
-      <c r="L15">
-        <v>-1</v>
-      </c>
-      <c r="M15">
-        <v>-1</v>
-      </c>
-      <c r="N15">
-        <v>-1</v>
-      </c>
-      <c r="O15">
-        <v>-1</v>
-      </c>
-      <c r="P15">
-        <v>-1</v>
-      </c>
-      <c r="Q15">
-        <v>-1</v>
-      </c>
-      <c r="R15">
-        <v>-1</v>
-      </c>
-      <c r="S15">
-        <v>-1</v>
-      </c>
-      <c r="T15">
-        <v>5</v>
-      </c>
-      <c r="U15">
-        <v>9</v>
-      </c>
-      <c r="V15">
-        <v>9</v>
-      </c>
       <c r="W15">
         <v>9</v>
       </c>
@@ -1633,160 +1612,6 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
-      <c r="E16">
-        <v>9</v>
-      </c>
-      <c r="F16">
-        <v>6</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <v>-1</v>
-      </c>
-      <c r="I16">
-        <v>-1</v>
-      </c>
-      <c r="J16">
-        <v>-1</v>
-      </c>
-      <c r="K16">
-        <v>-1</v>
-      </c>
-      <c r="L16">
-        <v>-1</v>
-      </c>
-      <c r="M16">
-        <v>-1</v>
-      </c>
-      <c r="N16">
-        <v>-1</v>
-      </c>
-      <c r="O16">
-        <v>-1</v>
-      </c>
-      <c r="P16">
-        <v>-1</v>
-      </c>
-      <c r="Q16">
-        <v>-1</v>
-      </c>
-      <c r="R16">
-        <v>-1</v>
-      </c>
-      <c r="S16">
-        <v>-1</v>
-      </c>
-      <c r="T16">
-        <v>5</v>
-      </c>
-      <c r="U16">
-        <v>6</v>
-      </c>
-      <c r="V16">
-        <v>5</v>
-      </c>
-      <c r="W16">
-        <v>9</v>
-      </c>
-      <c r="X16">
-        <v>6</v>
-      </c>
-      <c r="Y16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>8</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>9</v>
-      </c>
-      <c r="F17">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>9</v>
-      </c>
-      <c r="H17">
-        <v>-1</v>
-      </c>
-      <c r="I17">
-        <v>-1</v>
-      </c>
-      <c r="J17">
-        <v>-1</v>
-      </c>
-      <c r="K17">
-        <v>-1</v>
-      </c>
-      <c r="L17">
-        <v>-1</v>
-      </c>
-      <c r="M17">
-        <v>-1</v>
-      </c>
-      <c r="N17">
-        <v>-1</v>
-      </c>
-      <c r="O17">
-        <v>-1</v>
-      </c>
-      <c r="P17">
-        <v>-1</v>
-      </c>
-      <c r="Q17">
-        <v>-1</v>
-      </c>
-      <c r="R17">
-        <v>-1</v>
-      </c>
-      <c r="S17">
-        <v>-1</v>
-      </c>
-      <c r="T17">
-        <v>5</v>
-      </c>
-      <c r="U17">
-        <v>8</v>
-      </c>
-      <c r="V17">
-        <v>7</v>
-      </c>
-      <c r="W17">
-        <v>9</v>
-      </c>
-      <c r="X17">
-        <v>9</v>
-      </c>
-      <c r="Y17">
         <v>9</v>
       </c>
     </row>
@@ -1803,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1812,7 +1637,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1820,7 +1645,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1828,7 +1653,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -2082,58 +1907,58 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2203,7 +2028,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -2221,7 +2046,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2239,7 +2064,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2259,58 +2084,58 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2333,7 +2158,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -2351,7 +2176,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -2369,7 +2194,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2389,7 +2214,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -2407,7 +2232,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -2425,7 +2250,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2439,7 +2264,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2451,13 +2276,13 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -2469,13 +2294,13 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>100</v>
       </c>
       <c r="O13">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -2487,7 +2312,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>85</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2510,7 +2335,7 @@
         <v>95</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H14">
         <v>100</v>
@@ -2528,7 +2353,7 @@
         <v>95</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -2546,7 +2371,7 @@
         <v>95</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2557,7 +2382,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -2575,7 +2400,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -2593,7 +2418,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2605,124 +2430,6 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
-      <c r="C16">
-        <v>100</v>
-      </c>
-      <c r="D16">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-      <c r="F16">
-        <v>95</v>
-      </c>
-      <c r="G16">
-        <v>75</v>
-      </c>
-      <c r="H16">
-        <v>100</v>
-      </c>
-      <c r="I16">
-        <v>100</v>
-      </c>
-      <c r="J16">
-        <v>100</v>
-      </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>95</v>
-      </c>
-      <c r="M16">
-        <v>75</v>
-      </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>100</v>
-      </c>
-      <c r="P16">
-        <v>100</v>
-      </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>95</v>
-      </c>
-      <c r="S16">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17">
-        <v>100</v>
-      </c>
-      <c r="C17">
-        <v>100</v>
-      </c>
-      <c r="D17">
-        <v>100</v>
-      </c>
-      <c r="E17">
-        <v>100</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>100</v>
-      </c>
-      <c r="H17">
-        <v>100</v>
-      </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
-      <c r="J17">
-        <v>100</v>
-      </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
-      <c r="P17">
-        <v>100</v>
-      </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
-      <c r="S17">
         <v>100</v>
       </c>
     </row>
@@ -2751,31 +2458,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2783,7 +2490,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>14</v>
@@ -2815,7 +2522,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>14</v>
@@ -2847,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>14</v>
@@ -2879,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>14</v>
@@ -2911,7 +2618,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>14</v>
@@ -2943,7 +2650,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7">
         <v>14</v>
@@ -2977,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2986,262 +2693,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920140</v>
-      </c>
-      <c r="B3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920140</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920140</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920140</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920140</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920143</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920143</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920143</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920143</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920143</v>
-      </c>
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920143</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3260,22 +2727,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -3286,19 +2753,19 @@
         <v>21330051920139</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3309,19 +2776,19 @@
         <v>21330051920139</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3332,19 +2799,19 @@
         <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3355,19 +2822,19 @@
         <v>21330051920148</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3378,19 +2845,19 @@
         <v>21330051920138</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3401,19 +2868,19 @@
         <v>21330051920146</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3424,19 +2891,19 @@
         <v>21330051920150</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3447,19 +2914,19 @@
         <v>21330051920392</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9">
         <v>5</v>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -2493,7 +2493,7 @@
         <v>36</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -2502,19 +2502,19 @@
         <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="G2" s="2">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="H2">
         <v>5.3</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2525,7 +2525,7 @@
         <v>37</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>6</v>
@@ -2534,19 +2534,19 @@
         <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>6.3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2557,7 +2557,7 @@
         <v>38</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -2566,19 +2566,19 @@
         <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="G4" s="2">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="H4">
         <v>7.3</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2589,7 +2589,7 @@
         <v>39</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>12</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>7.6</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2621,7 +2621,7 @@
         <v>40</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>12</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -2639,10 +2639,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2653,7 +2653,7 @@
         <v>41</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>9.1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="60">
   <si>
     <t>Materia</t>
   </si>
@@ -128,15 +128,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Valerio González Valeria</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
@@ -158,55 +158,46 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -714,16 +705,16 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -756,10 +747,10 @@
         <v>6</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -791,16 +782,16 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -827,16 +818,16 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>9</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -868,16 +859,16 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -904,13 +895,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>8</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -945,16 +936,16 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -981,16 +972,16 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1022,16 +1013,16 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1058,16 +1049,16 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>5</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1099,16 +1090,16 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1135,16 +1126,16 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>6</v>
@@ -1176,16 +1167,16 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1212,13 +1203,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1253,16 +1244,16 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1289,7 +1280,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1298,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1330,16 +1321,16 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1366,16 +1357,16 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1407,16 +1398,16 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1443,7 +1434,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1452,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1484,16 +1475,16 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1523,13 +1514,13 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1561,16 +1552,16 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1597,16 +1588,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1748,10 +1739,10 @@
         <v>85</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -1766,10 +1757,10 @@
         <v>85</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O4">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -1810,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -1828,7 +1819,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -2046,7 +2037,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2064,7 +2055,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2105,7 +2096,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2123,7 +2114,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2161,10 +2152,10 @@
         <v>85</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I11">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -2179,10 +2170,10 @@
         <v>85</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O11">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2282,7 +2273,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -2300,7 +2291,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -2338,10 +2329,10 @@
         <v>75</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -2356,10 +2347,10 @@
         <v>75</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2400,7 +2391,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -2418,7 +2409,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2487,7 +2478,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -2496,19 +2487,19 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="G2" s="2">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2528,19 +2519,19 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G3" s="2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2551,7 +2542,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2560,19 +2551,19 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2668,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2718,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2750,7 +2741,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920139</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -2759,13 +2750,13 @@
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2773,7 +2764,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920139</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2782,13 +2773,13 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2796,7 +2787,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920148</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -2805,13 +2796,13 @@
         <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2819,7 +2810,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920148</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
         <v>47</v>
@@ -2828,13 +2819,13 @@
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2842,7 +2833,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920138</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
         <v>48</v>
@@ -2851,13 +2842,13 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -2865,19 +2856,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920146</v>
+        <v>21330051920147</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -2888,22 +2879,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920150</v>
+        <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -2911,24 +2902,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920392</v>
+        <v>21330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="52">
   <si>
     <t>Materia</t>
   </si>
@@ -128,6 +128,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -137,9 +140,6 @@
     <t>Valerio González Valeria</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -158,43 +158,19 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>ROGELIO</t>
@@ -717,10 +693,10 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -753,7 +729,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -794,10 +770,10 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -830,10 +806,10 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -871,10 +847,10 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -907,7 +883,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -948,10 +924,10 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -984,7 +960,7 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1025,10 +1001,10 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1061,10 +1037,10 @@
         <v>10</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1102,10 +1078,10 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1138,10 +1114,10 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1179,10 +1155,10 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1215,10 +1191,10 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1256,10 +1232,10 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1292,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1333,10 +1309,10 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1372,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1410,10 +1386,10 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1446,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1487,10 +1463,10 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1523,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1564,10 +1540,10 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1600,10 +1576,10 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +1730,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="N4">
         <v>95</v>
@@ -1772,7 +1748,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2167,7 +2143,7 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>95</v>
@@ -2185,7 +2161,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2223,7 +2199,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -2241,7 +2217,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2341,10 +2317,10 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M14">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N14">
         <v>95</v>
@@ -2359,10 +2335,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
-        <v>75</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2478,7 +2454,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -2499,7 +2475,7 @@
         <v>33.3</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2510,7 +2486,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -2531,7 +2507,7 @@
         <v>25</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2542,7 +2518,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2551,19 +2527,19 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2574,7 +2550,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2583,19 +2559,19 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2709,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2741,19 +2717,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920141</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
@@ -2764,19 +2740,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>36</v>
@@ -2787,162 +2763,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920141</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920147</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920382</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920382</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920148</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="56">
   <si>
     <t>Materia</t>
   </si>
@@ -65,6 +65,9 @@
     <t>FLORES MIXCOHA CRISTHIAN ALFONSO</t>
   </si>
   <si>
+    <t>GUTIERREZ FLORES MILKA SARAY</t>
+  </si>
+  <si>
     <t>HERNANDEZ ILLESCAS REDA ALAN</t>
   </si>
   <si>
@@ -131,12 +134,12 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Valerio González Valeria</t>
   </si>
   <si>
@@ -156,6 +159,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -535,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -894,40 +906,40 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H7">
         <v>9</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="M7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -951,19 +963,19 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -971,40 +983,40 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H8">
         <v>9</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1025,22 +1037,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1048,13 +1060,13 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1063,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>9</v>
@@ -1078,7 +1090,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1102,22 +1114,22 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1125,40 +1137,40 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>9</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1179,22 +1191,22 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1205,37 +1217,37 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>5</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1259,19 +1271,19 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1279,7 +1291,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1291,28 +1303,28 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <v>9</v>
       </c>
       <c r="I12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>6</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1336,19 +1348,19 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1359,19 +1371,19 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13">
         <v>9</v>
@@ -1380,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1389,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1413,19 +1425,19 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1433,40 +1445,40 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14">
         <v>9</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1487,22 +1499,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1513,37 +1525,37 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>9</v>
       </c>
       <c r="F15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1564,21 +1576,98 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>8</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16">
+        <v>6</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>-1</v>
+      </c>
+      <c r="O16">
+        <v>-1</v>
+      </c>
+      <c r="P16">
+        <v>-1</v>
+      </c>
+      <c r="Q16">
+        <v>-1</v>
+      </c>
+      <c r="R16">
+        <v>-1</v>
+      </c>
+      <c r="S16">
+        <v>-1</v>
+      </c>
+      <c r="T16">
+        <v>7</v>
+      </c>
+      <c r="U16">
+        <v>9</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
+      <c r="X16">
+        <v>8</v>
+      </c>
+      <c r="Y16">
         <v>10</v>
       </c>
     </row>
@@ -1595,7 +1684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1604,7 +1693,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1612,7 +1701,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1620,7 +1709,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -1880,13 +1969,13 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>100</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -1898,13 +1987,13 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -1916,13 +2005,13 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -1995,7 +2084,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -2013,7 +2102,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2031,7 +2120,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2054,7 +2143,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -2072,7 +2161,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2090,7 +2179,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2113,7 +2202,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
@@ -2125,13 +2214,13 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -2143,13 +2232,13 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2161,7 +2250,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2172,7 +2261,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -2181,16 +2270,16 @@
         <v>100</v>
       </c>
       <c r="F12">
+        <v>100</v>
+      </c>
+      <c r="G12">
+        <v>85</v>
+      </c>
+      <c r="H12">
         <v>95</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
       <c r="I12">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -2199,16 +2288,16 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O12">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -2217,10 +2306,10 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2231,7 +2320,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
@@ -2240,7 +2329,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -2249,7 +2338,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -2258,7 +2347,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -2267,7 +2356,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -2276,7 +2365,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -2290,7 +2379,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -2299,16 +2388,16 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G14">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -2317,16 +2406,16 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="M14">
-        <v>75.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2335,10 +2424,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>75.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2358,45 +2447,104 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I15">
+        <v>88</v>
+      </c>
+      <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>97.5</v>
+      </c>
+      <c r="M15">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="N15">
+        <v>95</v>
+      </c>
+      <c r="O15">
+        <v>88</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>97.5</v>
+      </c>
+      <c r="S15">
+        <v>75.59999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>100</v>
+      </c>
+      <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>100</v>
+      </c>
+      <c r="F16">
+        <v>100</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
         <v>98</v>
       </c>
-      <c r="J15">
-        <v>100</v>
-      </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
+        <v>100</v>
+      </c>
+      <c r="M16">
+        <v>100</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
         <v>98</v>
       </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>100</v>
-      </c>
-      <c r="S15">
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
         <v>100</v>
       </c>
     </row>
@@ -2425,31 +2573,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2457,10 +2605,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -2469,30 +2617,30 @@
         <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="G2" s="2">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="H2">
         <v>6.9</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>9</v>
@@ -2501,45 +2649,45 @@
         <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="G3" s="2">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2553,25 +2701,25 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2585,25 +2733,25 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>12</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2617,13 +2765,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2635,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2651,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2660,22 +2808,62 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>21330051920140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>21330051920140</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2694,22 +2882,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -2720,13 +2908,13 @@
         <v>21330051920141</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -2743,19 +2931,19 @@
         <v>21330051920141</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2766,13 +2954,13 @@
         <v>21330051920148</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="59">
   <si>
     <t>Materia</t>
   </si>
@@ -134,15 +134,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -170,22 +170,31 @@
     <t>MILKA SARAY</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>GALICIA</t>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
   </si>
   <si>
     <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
   </si>
 </sst>
 </file>
@@ -711,28 +720,28 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>5</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -744,7 +753,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -788,31 +797,31 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -865,28 +874,28 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -912,7 +921,7 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -930,7 +939,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -942,31 +951,31 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -975,7 +984,7 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1019,22 +1028,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1096,31 +1105,31 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1129,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1173,31 +1182,31 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1250,25 +1259,25 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>9</v>
@@ -1327,28 +1336,28 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1360,7 +1369,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1404,31 +1413,31 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>8</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1437,7 +1446,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1481,22 +1490,22 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1558,22 +1567,22 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
@@ -1635,31 +1644,31 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>9</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1822,10 +1831,10 @@
         <v>84.40000000000001</v>
       </c>
       <c r="N4">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>87.5</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -1837,7 +1846,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>84.40000000000001</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1884,7 +1893,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -1969,7 +1978,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -1987,7 +1996,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -2005,7 +2014,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2179,7 +2188,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>94</v>
+        <v>88.8</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2238,7 +2247,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2294,10 +2303,10 @@
         <v>80</v>
       </c>
       <c r="N12">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="O12">
-        <v>82</v>
+        <v>88.8</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -2309,7 +2318,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2415,7 +2424,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2471,10 +2480,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="O15">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2486,7 +2495,7 @@
         <v>97.5</v>
       </c>
       <c r="S15">
-        <v>75.59999999999999</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -2533,7 +2542,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -2634,7 +2643,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -2643,30 +2652,30 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
@@ -2675,19 +2684,19 @@
         <v>13</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>76.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2698,7 +2707,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
@@ -2707,19 +2716,19 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>84.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G5" s="2">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2739,19 +2748,19 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>7.7</v>
-      </c>
-      <c r="H6">
-        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2799,7 +2808,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2840,29 +2849,9 @@
         <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920140</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2873,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2905,19 +2894,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
@@ -2928,16 +2917,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2951,24 +2940,116 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920148</v>
+        <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920140</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920147</v>
+      </c>
+      <c r="B6" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920147</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4">
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="56">
   <si>
     <t>Materia</t>
   </si>
@@ -131,15 +131,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Valerio González Valeria</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Valerio González Valeria</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -161,40 +161,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
   </si>
 </sst>
 </file>
@@ -732,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -750,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -809,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -886,7 +877,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -927,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -945,7 +936,7 @@
         <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -963,7 +954,7 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -981,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1040,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1117,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1135,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1194,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1271,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1348,7 +1339,7 @@
         <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>9</v>
@@ -1425,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>7</v>
@@ -1502,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1579,7 +1570,7 @@
         <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
         <v>5</v>
@@ -1656,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1843,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>90.7</v>
@@ -1984,7 +1975,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>100</v>
@@ -2002,7 +1993,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -2020,7 +2011,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2315,7 +2306,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
         <v>88</v>
@@ -2374,7 +2365,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -2492,7 +2483,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
       <c r="S15">
         <v>85.3</v>
@@ -2611,7 +2602,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
@@ -2620,30 +2611,30 @@
         <v>13</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>61.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>38</v>
@@ -2664,7 +2655,7 @@
         <v>15.4</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2675,7 +2666,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
@@ -2696,7 +2687,7 @@
         <v>15.4</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2808,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2835,26 +2826,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2862,7 +2833,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2894,19 +2865,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" t="s">
-        <v>56</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>38</v>
@@ -2917,22 +2888,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
         <v>50</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" t="s">
-        <v>56</v>
-      </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2940,22 +2911,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2966,90 +2937,21 @@
         <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920147</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -732,19 +732,19 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -806,19 +806,19 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -883,22 +883,22 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -960,22 +960,22 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1037,19 +1037,19 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1114,22 +1114,22 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1191,22 +1191,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1268,19 +1268,19 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1345,22 +1345,22 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1422,22 +1422,22 @@
         <v>7</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1499,22 +1499,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1653,19 +1653,19 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -2623,7 +2623,7 @@
         <v>15.4</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>15.4</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>7.7</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ASV - Estadisticos 20231.xlsx
+++ b/grupos/5ASV - Estadisticos 20231.xlsx
@@ -732,19 +732,19 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -806,19 +806,19 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -883,22 +883,22 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -960,22 +960,22 @@
         <v>8</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1037,19 +1037,19 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1114,22 +1114,22 @@
         <v>5</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1191,22 +1191,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1268,19 +1268,19 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1345,22 +1345,22 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1422,22 +1422,22 @@
         <v>7</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1499,22 +1499,22 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1653,19 +1653,19 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -2623,7 +2623,7 @@
         <v>15.4</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>15.4</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>15.4</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2719,7 +2719,7 @@
         <v>7.7</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
